--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ARKANSAS_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ARKANSAS_2011.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C103">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C126">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C419">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C454">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C695">
